--- a/Thesis Forecasting/metadata/rbfnn/validation_daily_metrics.xlsx
+++ b/Thesis Forecasting/metadata/rbfnn/validation_daily_metrics.xlsx
@@ -494,13 +494,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2.769769282932541</v>
+        <v>2.770276798676984</v>
       </c>
       <c r="D3" t="n">
-        <v>1.6284</v>
+        <v>1.628804717378131</v>
       </c>
       <c r="E3" t="n">
-        <v>2.049742764450375</v>
+        <v>2.048262084241264</v>
       </c>
       <c r="F3" t="n">
         <v>24</v>
@@ -516,13 +516,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>5.990415563137147</v>
+        <v>5.964898291863569</v>
       </c>
       <c r="D4" t="n">
-        <v>2.995233310976742</v>
+        <v>2.98525469936643</v>
       </c>
       <c r="E4" t="n">
-        <v>4.726825660508419</v>
+        <v>4.700248022900412</v>
       </c>
       <c r="F4" t="n">
         <v>24</v>
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>2.376019939039683</v>
+        <v>2.370963037251132</v>
       </c>
       <c r="D5" t="n">
-        <v>1.404131083333334</v>
+        <v>1.401365325915964</v>
       </c>
       <c r="E5" t="n">
-        <v>1.983174763705367</v>
+        <v>1.976088165316986</v>
       </c>
       <c r="F5" t="n">
         <v>24</v>
@@ -560,13 +560,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>2.64592858149083</v>
+        <v>2.645064468618645</v>
       </c>
       <c r="D6" t="n">
-        <v>1.565502083333334</v>
+        <v>1.565093368020219</v>
       </c>
       <c r="E6" t="n">
-        <v>1.810159446677512</v>
+        <v>1.811820324655839</v>
       </c>
       <c r="F6" t="n">
         <v>24</v>
@@ -582,13 +582,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>2.935685031982242</v>
+        <v>2.936141698489123</v>
       </c>
       <c r="D7" t="n">
-        <v>1.746152083333334</v>
+        <v>1.746381057618186</v>
       </c>
       <c r="E7" t="n">
-        <v>2.446396333004698</v>
+        <v>2.442020659642461</v>
       </c>
       <c r="F7" t="n">
         <v>24</v>
@@ -604,13 +604,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>4.726641841554042</v>
+        <v>4.72420336249248</v>
       </c>
       <c r="D8" t="n">
-        <v>2.314945833333334</v>
+        <v>2.313533219990693</v>
       </c>
       <c r="E8" t="n">
-        <v>4.580323870190113</v>
+        <v>4.58021870563817</v>
       </c>
       <c r="F8" t="n">
         <v>24</v>
@@ -626,13 +626,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3.689693741251379</v>
+        <v>3.613157566292534</v>
       </c>
       <c r="D9" t="n">
-        <v>2.156716500009701</v>
+        <v>2.111598931278538</v>
       </c>
       <c r="E9" t="n">
-        <v>3.354811687098174</v>
+        <v>3.347539565997543</v>
       </c>
       <c r="F9" t="n">
         <v>24</v>
@@ -648,13 +648,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>2.891203027862839</v>
+        <v>2.888672855905765</v>
       </c>
       <c r="D10" t="n">
-        <v>1.7562165</v>
+        <v>1.754659998909474</v>
       </c>
       <c r="E10" t="n">
-        <v>2.359048436946346</v>
+        <v>2.35398380771455</v>
       </c>
       <c r="F10" t="n">
         <v>24</v>
@@ -670,13 +670,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>2.368558128279196</v>
+        <v>2.368558219074338</v>
       </c>
       <c r="D11" t="n">
-        <v>1.448391666666667</v>
+        <v>1.448392035509212</v>
       </c>
       <c r="E11" t="n">
-        <v>1.628658580767723</v>
+        <v>1.628666535170433</v>
       </c>
       <c r="F11" t="n">
         <v>24</v>
@@ -692,13 +692,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>2.233729908697475</v>
+        <v>2.233774153318198</v>
       </c>
       <c r="D12" t="n">
-        <v>1.339044083333332</v>
+        <v>1.339047510212354</v>
       </c>
       <c r="E12" t="n">
-        <v>1.6220372012885</v>
+        <v>1.621380406134187</v>
       </c>
       <c r="F12" t="n">
         <v>24</v>
@@ -714,13 +714,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>2.033023722150027</v>
+        <v>2.031756947726627</v>
       </c>
       <c r="D13" t="n">
-        <v>1.223214916666667</v>
+        <v>1.222430180973133</v>
       </c>
       <c r="E13" t="n">
-        <v>1.521516551806837</v>
+        <v>1.520320087186771</v>
       </c>
       <c r="F13" t="n">
         <v>24</v>
@@ -736,13 +736,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>5.069978730668288</v>
+        <v>5.060136705552954</v>
       </c>
       <c r="D14" t="n">
-        <v>2.646793916666668</v>
+        <v>2.643167329227337</v>
       </c>
       <c r="E14" t="n">
-        <v>4.302422193943566</v>
+        <v>4.290128130086874</v>
       </c>
       <c r="F14" t="n">
         <v>24</v>
@@ -758,13 +758,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5.462111091116669</v>
+        <v>5.469768470796742</v>
       </c>
       <c r="D15" t="n">
-        <v>2.938614583333333</v>
+        <v>2.943648300914838</v>
       </c>
       <c r="E15" t="n">
-        <v>4.68317325408878</v>
+        <v>4.696307543568611</v>
       </c>
       <c r="F15" t="n">
         <v>24</v>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>3.3339507279013</v>
+        <v>3.316544809567497</v>
       </c>
       <c r="D16" t="n">
-        <v>1.888670668699083</v>
+        <v>1.881043360406186</v>
       </c>
       <c r="E16" t="n">
-        <v>2.994046251151211</v>
+        <v>2.980240330975831</v>
       </c>
       <c r="F16" t="n">
         <v>24</v>
@@ -802,13 +802,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>2.519255034251971</v>
+        <v>2.516186670704151</v>
       </c>
       <c r="D17" t="n">
-        <v>1.5409625</v>
+        <v>1.539164709125334</v>
       </c>
       <c r="E17" t="n">
-        <v>1.79333319431536</v>
+        <v>1.793173612776342</v>
       </c>
       <c r="F17" t="n">
         <v>24</v>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3.045145224159311</v>
+        <v>3.046277141275689</v>
       </c>
       <c r="D18" t="n">
-        <v>1.823983333333332</v>
+        <v>1.824619566342791</v>
       </c>
       <c r="E18" t="n">
-        <v>2.22951126613734</v>
+        <v>2.225420274688549</v>
       </c>
       <c r="F18" t="n">
         <v>24</v>
@@ -846,13 +846,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>2.579882626950697</v>
+        <v>2.577977464071519</v>
       </c>
       <c r="D19" t="n">
-        <v>1.586856416666668</v>
+        <v>1.585663426005007</v>
       </c>
       <c r="E19" t="n">
-        <v>1.792698261094108</v>
+        <v>1.790683350476925</v>
       </c>
       <c r="F19" t="n">
         <v>24</v>
@@ -868,13 +868,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>4.155654188631613</v>
+        <v>4.161557469272426</v>
       </c>
       <c r="D20" t="n">
-        <v>2.406147916666666</v>
+        <v>2.40979626430273</v>
       </c>
       <c r="E20" t="n">
-        <v>3.371086676321277</v>
+        <v>3.376107812889935</v>
       </c>
       <c r="F20" t="n">
         <v>24</v>
@@ -890,13 +890,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3.183610740449461</v>
+        <v>3.18367279305633</v>
       </c>
       <c r="D21" t="n">
-        <v>1.919625000000001</v>
+        <v>1.919625594727074</v>
       </c>
       <c r="E21" t="n">
-        <v>2.268325577748191</v>
+        <v>2.268105418454356</v>
       </c>
       <c r="F21" t="n">
         <v>24</v>
@@ -912,13 +912,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>5.858050071795446</v>
+        <v>5.854932738164476</v>
       </c>
       <c r="D22" t="n">
-        <v>3.117202250000001</v>
+        <v>3.115261041113274</v>
       </c>
       <c r="E22" t="n">
-        <v>4.486896691969275</v>
+        <v>4.483670883597072</v>
       </c>
       <c r="F22" t="n">
         <v>24</v>
@@ -934,13 +934,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>8.891089992896527</v>
+        <v>8.899550106189203</v>
       </c>
       <c r="D23" t="n">
-        <v>4.4865665</v>
+        <v>4.488761561863154</v>
       </c>
       <c r="E23" t="n">
-        <v>7.544787704109089</v>
+        <v>7.549439941228674</v>
       </c>
       <c r="F23" t="n">
         <v>24</v>
@@ -956,13 +956,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1.670573374854143</v>
+        <v>1.668449615087587</v>
       </c>
       <c r="D24" t="n">
-        <v>1.0064</v>
+        <v>1.005206676312907</v>
       </c>
       <c r="E24" t="n">
-        <v>1.41016394532988</v>
+        <v>1.408104227986746</v>
       </c>
       <c r="F24" t="n">
         <v>24</v>
@@ -978,13 +978,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>2.722513984173261</v>
+        <v>2.723235864235152</v>
       </c>
       <c r="D25" t="n">
-        <v>1.6213455</v>
+        <v>1.621760759639234</v>
       </c>
       <c r="E25" t="n">
-        <v>1.92273260804157</v>
+        <v>1.923212387038118</v>
       </c>
       <c r="F25" t="n">
         <v>24</v>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>2.48875222316728</v>
+        <v>2.493178831246599</v>
       </c>
       <c r="D26" t="n">
-        <v>1.497445999999999</v>
+        <v>1.500138943086101</v>
       </c>
       <c r="E26" t="n">
-        <v>1.864713023356587</v>
+        <v>1.867723041964766</v>
       </c>
       <c r="F26" t="n">
         <v>24</v>
@@ -1022,13 +1022,13 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>2.307426198423384</v>
+        <v>2.301800985663564</v>
       </c>
       <c r="D27" t="n">
-        <v>1.393283166666667</v>
+        <v>1.390058924113988</v>
       </c>
       <c r="E27" t="n">
-        <v>1.624368358516831</v>
+        <v>1.623787784439135</v>
       </c>
       <c r="F27" t="n">
         <v>24</v>
@@ -1044,13 +1044,13 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>6.848111875095259</v>
+        <v>6.848506845658976</v>
       </c>
       <c r="D28" t="n">
-        <v>2.275333333333333</v>
+        <v>2.275467759114379</v>
       </c>
       <c r="E28" t="n">
-        <v>6.195746983701129</v>
+        <v>6.196155127169215</v>
       </c>
       <c r="F28" t="n">
         <v>24</v>
@@ -1088,13 +1088,13 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>5.185244187945445</v>
+        <v>5.177908465548975</v>
       </c>
       <c r="D30" t="n">
-        <v>2.115472916666667</v>
+        <v>2.111321712120498</v>
       </c>
       <c r="E30" t="n">
-        <v>4.033478032394933</v>
+        <v>4.029795117186008</v>
       </c>
       <c r="F30" t="n">
         <v>24</v>
@@ -1110,13 +1110,13 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>5.913753329926657e-15</v>
+        <v>3.100698783472521e-09</v>
       </c>
       <c r="D31" t="n">
-        <v>3.552713678800501e-15</v>
+        <v>1.862646925587796e-09</v>
       </c>
       <c r="E31" t="n">
-        <v>5.426859785202775e-15</v>
+        <v>4.02377327139191e-09</v>
       </c>
       <c r="F31" t="n">
         <v>24</v>
@@ -1132,13 +1132,13 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>3.807182563351272</v>
+        <v>3.801407933956386</v>
       </c>
       <c r="D32" t="n">
-        <v>2.197870666666666</v>
+        <v>2.194500707837902</v>
       </c>
       <c r="E32" t="n">
-        <v>2.576080370766926</v>
+        <v>2.573181754224787</v>
       </c>
       <c r="F32" t="n">
         <v>24</v>
@@ -1154,13 +1154,13 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>2.889701422083271</v>
+        <v>2.87886744176702</v>
       </c>
       <c r="D33" t="n">
-        <v>1.675902083333334</v>
+        <v>1.669670737086176</v>
       </c>
       <c r="E33" t="n">
-        <v>2.070289288083714</v>
+        <v>2.065927694465207</v>
       </c>
       <c r="F33" t="n">
         <v>24</v>
@@ -1176,13 +1176,13 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>3.871288977410411</v>
+        <v>3.887337268820505</v>
       </c>
       <c r="D34" t="n">
-        <v>2.142964606116782</v>
+        <v>2.152233389432161</v>
       </c>
       <c r="E34" t="n">
-        <v>2.915623994102713</v>
+        <v>2.934664605849165</v>
       </c>
       <c r="F34" t="n">
         <v>24</v>
@@ -1198,13 +1198,13 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>4.012812975131519</v>
+        <v>4.0019646434903</v>
       </c>
       <c r="D35" t="n">
-        <v>2.297595666666667</v>
+        <v>2.29141954858548</v>
       </c>
       <c r="E35" t="n">
-        <v>2.838367118978915</v>
+        <v>2.834317694844473</v>
       </c>
       <c r="F35" t="n">
         <v>24</v>
@@ -1220,13 +1220,13 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>3.154875204773769</v>
+        <v>3.162628166321865</v>
       </c>
       <c r="D36" t="n">
-        <v>1.817672916666665</v>
+        <v>1.822347560213318</v>
       </c>
       <c r="E36" t="n">
-        <v>2.683887616581121</v>
+        <v>2.697079429028259</v>
       </c>
       <c r="F36" t="n">
         <v>24</v>
@@ -1242,13 +1242,13 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2.705807793252593</v>
+        <v>2.710149769336643</v>
       </c>
       <c r="D37" t="n">
-        <v>1.556722916666666</v>
+        <v>1.559307949074666</v>
       </c>
       <c r="E37" t="n">
-        <v>1.934059572801684</v>
+        <v>1.93511768347417</v>
       </c>
       <c r="F37" t="n">
         <v>24</v>
@@ -1264,13 +1264,13 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>4.858983121407396</v>
+        <v>4.862070951773615</v>
       </c>
       <c r="D38" t="n">
-        <v>2.442914583333335</v>
+        <v>2.444759406130699</v>
       </c>
       <c r="E38" t="n">
-        <v>3.539905050000753</v>
+        <v>3.540979595430422</v>
       </c>
       <c r="F38" t="n">
         <v>24</v>
@@ -1286,13 +1286,13 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>3.481955565964328</v>
+        <v>3.460499381816927</v>
       </c>
       <c r="D39" t="n">
-        <v>1.795158310976741</v>
+        <v>1.785181763836944</v>
       </c>
       <c r="E39" t="n">
-        <v>2.662770352265093</v>
+        <v>2.646684561180536</v>
       </c>
       <c r="F39" t="n">
         <v>24</v>
@@ -1308,13 +1308,13 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>2.172050056571554</v>
+        <v>2.175698696641363</v>
       </c>
       <c r="D40" t="n">
-        <v>1.30613975</v>
+        <v>1.308350056798791</v>
       </c>
       <c r="E40" t="n">
-        <v>1.664753030849171</v>
+        <v>1.666901323547664</v>
       </c>
       <c r="F40" t="n">
         <v>24</v>
@@ -1330,13 +1330,13 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>2.179384645155367</v>
+        <v>2.182376396661708</v>
       </c>
       <c r="D41" t="n">
-        <v>1.306812666666668</v>
+        <v>1.308620463050193</v>
       </c>
       <c r="E41" t="n">
-        <v>1.658093321906422</v>
+        <v>1.660067922012709</v>
       </c>
       <c r="F41" t="n">
         <v>24</v>
@@ -1352,13 +1352,13 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>1.55253205738285</v>
+        <v>1.499250501669465</v>
       </c>
       <c r="D42" t="n">
-        <v>0.942981416666667</v>
+        <v>0.9112130257903625</v>
       </c>
       <c r="E42" t="n">
-        <v>1.478948851652699</v>
+        <v>1.473028787483723</v>
       </c>
       <c r="F42" t="n">
         <v>24</v>
@@ -1374,13 +1374,13 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>2.399015769591562</v>
+        <v>2.399030229349171</v>
       </c>
       <c r="D43" t="n">
-        <v>1.466833333333331</v>
+        <v>1.46684233666149</v>
       </c>
       <c r="E43" t="n">
-        <v>1.773083131100079</v>
+        <v>1.773096405997835</v>
       </c>
       <c r="F43" t="n">
         <v>24</v>
@@ -1396,13 +1396,13 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>2.613030487593739</v>
+        <v>2.630584313370755</v>
       </c>
       <c r="D44" t="n">
-        <v>1.502437499796274</v>
+        <v>1.511985290342102</v>
       </c>
       <c r="E44" t="n">
-        <v>2.035920872440131</v>
+        <v>2.044242304147884</v>
       </c>
       <c r="F44" t="n">
         <v>24</v>
@@ -1418,13 +1418,13 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>3.011996125522213</v>
+        <v>3.00754016433823</v>
       </c>
       <c r="D45" t="n">
-        <v>1.822218750000001</v>
+        <v>1.819598047238899</v>
       </c>
       <c r="E45" t="n">
-        <v>2.070077884026952</v>
+        <v>2.069025587502059</v>
       </c>
       <c r="F45" t="n">
         <v>24</v>
@@ -1440,13 +1440,13 @@
         </is>
       </c>
       <c r="C46" t="n">
-        <v>4.465042674774895</v>
+        <v>4.436272216805706</v>
       </c>
       <c r="D46" t="n">
-        <v>2.390843749359714</v>
+        <v>2.375478851138136</v>
       </c>
       <c r="E46" t="n">
-        <v>2.845969754330056</v>
+        <v>2.847757509527544</v>
       </c>
       <c r="F46" t="n">
         <v>24</v>
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>2.858633557731081</v>
+        <v>2.849723660617371</v>
       </c>
       <c r="D47" t="n">
-        <v>1.557795832343807</v>
+        <v>1.553007777555475</v>
       </c>
       <c r="E47" t="n">
-        <v>1.981364031660642</v>
+        <v>1.982872325712339</v>
       </c>
       <c r="F47" t="n">
         <v>24</v>
@@ -1484,13 +1484,13 @@
         </is>
       </c>
       <c r="C48" t="n">
-        <v>3.317183104268436</v>
+        <v>3.306188945473349</v>
       </c>
       <c r="D48" t="n">
-        <v>1.784208332130375</v>
+        <v>1.779881901545478</v>
       </c>
       <c r="E48" t="n">
-        <v>2.133429921024288</v>
+        <v>2.143575948371692</v>
       </c>
       <c r="F48" t="n">
         <v>24</v>
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="C49" t="n">
-        <v>4.039396476099514</v>
+        <v>4.040585072201518</v>
       </c>
       <c r="D49" t="n">
-        <v>2.190575000000002</v>
+        <v>2.190968913683235</v>
       </c>
       <c r="E49" t="n">
-        <v>2.826538856313496</v>
+        <v>2.824201648621194</v>
       </c>
       <c r="F49" t="n">
         <v>24</v>
@@ -1528,13 +1528,13 @@
         </is>
       </c>
       <c r="C50" t="n">
-        <v>4.368145389586679</v>
+        <v>4.378364939138696</v>
       </c>
       <c r="D50" t="n">
-        <v>2.388183329331556</v>
+        <v>2.39385853859422</v>
       </c>
       <c r="E50" t="n">
-        <v>2.794291915336297</v>
+        <v>2.806941261484447</v>
       </c>
       <c r="F50" t="n">
         <v>24</v>
@@ -1550,13 +1550,13 @@
         </is>
       </c>
       <c r="C51" t="n">
-        <v>3.859011802445961</v>
+        <v>3.856514907570294</v>
       </c>
       <c r="D51" t="n">
-        <v>2.108881248200414</v>
+        <v>2.107821028364982</v>
       </c>
       <c r="E51" t="n">
-        <v>2.687543985254541</v>
+        <v>2.698492962817251</v>
       </c>
       <c r="F51" t="n">
         <v>24</v>
@@ -1572,13 +1572,13 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>3.524042559748416</v>
+        <v>3.52190253010276</v>
       </c>
       <c r="D52" t="n">
-        <v>1.914389583343035</v>
+        <v>1.913504372205524</v>
       </c>
       <c r="E52" t="n">
-        <v>2.260893532244967</v>
+        <v>2.264628045025576</v>
       </c>
       <c r="F52" t="n">
         <v>24</v>
@@ -1594,13 +1594,13 @@
         </is>
       </c>
       <c r="C53" t="n">
-        <v>3.869555868830504</v>
+        <v>3.783801823498008</v>
       </c>
       <c r="D53" t="n">
-        <v>2.07536458331393</v>
+        <v>2.028656211182536</v>
       </c>
       <c r="E53" t="n">
-        <v>2.474835292876577</v>
+        <v>2.45670185568369</v>
       </c>
       <c r="F53" t="n">
         <v>24</v>
@@ -1616,13 +1616,13 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>3.957860571194265</v>
+        <v>3.952325135363917</v>
       </c>
       <c r="D54" t="n">
-        <v>1.985152088601125</v>
+        <v>1.982871873573822</v>
       </c>
       <c r="E54" t="n">
-        <v>2.330028143027498</v>
+        <v>2.328754762287676</v>
       </c>
       <c r="F54" t="n">
         <v>24</v>
@@ -1638,13 +1638,13 @@
         </is>
       </c>
       <c r="C55" t="n">
-        <v>2.941249770734507</v>
+        <v>2.981018859601553</v>
       </c>
       <c r="D55" t="n">
-        <v>1.488202084841879</v>
+        <v>1.50961880393582</v>
       </c>
       <c r="E55" t="n">
-        <v>1.87208861339294</v>
+        <v>1.876686563516776</v>
       </c>
       <c r="F55" t="n">
         <v>24</v>
@@ -1660,13 +1660,13 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>3.229474292726101</v>
+        <v>3.27182820772618</v>
       </c>
       <c r="D56" t="n">
-        <v>1.677743770561855</v>
+        <v>1.699321674716756</v>
       </c>
       <c r="E56" t="n">
-        <v>1.947392134629561</v>
+        <v>1.975865198688197</v>
       </c>
       <c r="F56" t="n">
         <v>24</v>
@@ -1682,13 +1682,13 @@
         </is>
       </c>
       <c r="C57" t="n">
-        <v>3.827901246015399</v>
+        <v>3.884471190503104</v>
       </c>
       <c r="D57" t="n">
-        <v>1.934575041220723</v>
+        <v>1.96443514585458</v>
       </c>
       <c r="E57" t="n">
-        <v>2.278201651881534</v>
+        <v>2.301892863801981</v>
       </c>
       <c r="F57" t="n">
         <v>24</v>
@@ -1704,13 +1704,13 @@
         </is>
       </c>
       <c r="C58" t="n">
-        <v>9.068307178251134</v>
+        <v>9.093546939932013</v>
       </c>
       <c r="D58" t="n">
-        <v>3.511645828041286</v>
+        <v>3.525115090338848</v>
       </c>
       <c r="E58" t="n">
-        <v>6.021529183371657</v>
+        <v>6.025544844677375</v>
       </c>
       <c r="F58" t="n">
         <v>24</v>
@@ -1726,13 +1726,13 @@
         </is>
       </c>
       <c r="C59" t="n">
-        <v>3.213088828677097</v>
+        <v>3.28610731233812</v>
       </c>
       <c r="D59" t="n">
-        <v>1.686358380675564</v>
+        <v>1.727417991508009</v>
       </c>
       <c r="E59" t="n">
-        <v>2.156660074748188</v>
+        <v>2.173730839197199</v>
       </c>
       <c r="F59" t="n">
         <v>24</v>
@@ -1748,13 +1748,13 @@
         </is>
       </c>
       <c r="C60" t="n">
-        <v>3.219874761201581</v>
+        <v>3.249995864775537</v>
       </c>
       <c r="D60" t="n">
-        <v>1.647293796619485</v>
+        <v>1.663555967765224</v>
       </c>
       <c r="E60" t="n">
-        <v>1.938647119858478</v>
+        <v>1.953544744286807</v>
       </c>
       <c r="F60" t="n">
         <v>24</v>
@@ -1770,13 +1770,13 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>3.838809934239046</v>
+        <v>3.827349615489072</v>
       </c>
       <c r="D61" t="n">
-        <v>1.939344831575948</v>
+        <v>1.934964040931798</v>
       </c>
       <c r="E61" t="n">
-        <v>2.397581663980366</v>
+        <v>2.391718073969736</v>
       </c>
       <c r="F61" t="n">
         <v>24</v>
@@ -1792,13 +1792,13 @@
         </is>
       </c>
       <c r="C62" t="n">
-        <v>2.973645903517051</v>
+        <v>2.986358252246939</v>
       </c>
       <c r="D62" t="n">
-        <v>1.518266852499475</v>
+        <v>1.526314609601398</v>
       </c>
       <c r="E62" t="n">
-        <v>1.940974441735574</v>
+        <v>1.947239449934712</v>
       </c>
       <c r="F62" t="n">
         <v>24</v>
@@ -1814,13 +1814,13 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>2.855265815099933</v>
+        <v>2.850007172012023</v>
       </c>
       <c r="D63" t="n">
-        <v>1.454314685439271</v>
+        <v>1.453270949607779</v>
       </c>
       <c r="E63" t="n">
-        <v>1.739474619695434</v>
+        <v>1.739612680825118</v>
       </c>
       <c r="F63" t="n">
         <v>24</v>
@@ -1836,13 +1836,13 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>2.528696796404369</v>
+        <v>2.537335494378206</v>
       </c>
       <c r="D64" t="n">
-        <v>1.264270861598003</v>
+        <v>1.269191533035122</v>
       </c>
       <c r="E64" t="n">
-        <v>1.594730298990705</v>
+        <v>1.586564381549759</v>
       </c>
       <c r="F64" t="n">
         <v>24</v>
@@ -1858,13 +1858,13 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>3.00334914604039</v>
+        <v>2.949898703250974</v>
       </c>
       <c r="D65" t="n">
-        <v>1.515781160743403</v>
+        <v>1.488484057159572</v>
       </c>
       <c r="E65" t="n">
-        <v>1.871639010184367</v>
+        <v>1.877943741553803</v>
       </c>
       <c r="F65" t="n">
         <v>24</v>
@@ -1880,13 +1880,13 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>2.054892021995369</v>
+        <v>1.978606951630246</v>
       </c>
       <c r="D66" t="n">
-        <v>1.069843753327536</v>
+        <v>1.030136382663578</v>
       </c>
       <c r="E66" t="n">
-        <v>1.260431823119872</v>
+        <v>1.223040635006191</v>
       </c>
       <c r="F66" t="n">
         <v>24</v>
@@ -1902,13 +1902,13 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>3.962143410670102</v>
+        <v>3.900270599036143</v>
       </c>
       <c r="D67" t="n">
-        <v>1.978291839785952</v>
+        <v>1.946694851117271</v>
       </c>
       <c r="E67" t="n">
-        <v>2.475287830730117</v>
+        <v>2.456326839659394</v>
       </c>
       <c r="F67" t="n">
         <v>24</v>
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="C68" t="n">
-        <v>3.751017365578063</v>
+        <v>3.834641989058604</v>
       </c>
       <c r="D68" t="n">
-        <v>1.910264604647039</v>
+        <v>1.953389801554382</v>
       </c>
       <c r="E68" t="n">
-        <v>2.245420949281823</v>
+        <v>2.279005135132666</v>
       </c>
       <c r="F68" t="n">
         <v>24</v>
@@ -1946,13 +1946,13 @@
         </is>
       </c>
       <c r="C69" t="n">
-        <v>3.401672965877296</v>
+        <v>3.415370579475087</v>
       </c>
       <c r="D69" t="n">
-        <v>1.713783304428381</v>
+        <v>1.722842334400312</v>
       </c>
       <c r="E69" t="n">
-        <v>2.265956090775131</v>
+        <v>2.263265229914369</v>
       </c>
       <c r="F69" t="n">
         <v>24</v>
@@ -1968,13 +1968,13 @@
         </is>
       </c>
       <c r="C70" t="n">
-        <v>3.636325954748688</v>
+        <v>3.668147632895528</v>
       </c>
       <c r="D70" t="n">
-        <v>1.908279163746584</v>
+        <v>1.925239928539073</v>
       </c>
       <c r="E70" t="n">
-        <v>2.269307289013229</v>
+        <v>2.290423660037717</v>
       </c>
       <c r="F70" t="n">
         <v>24</v>
@@ -1990,13 +1990,13 @@
         </is>
       </c>
       <c r="C71" t="n">
-        <v>2.153045600902503</v>
+        <v>2.156965208117106</v>
       </c>
       <c r="D71" t="n">
-        <v>1.112866669732268</v>
+        <v>1.115256108810379</v>
       </c>
       <c r="E71" t="n">
-        <v>1.321676550082064</v>
+        <v>1.326254079803084</v>
       </c>
       <c r="F71" t="n">
         <v>24</v>
@@ -2012,13 +2012,13 @@
         </is>
       </c>
       <c r="C72" t="n">
-        <v>4.084830279842316</v>
+        <v>4.045697295670467</v>
       </c>
       <c r="D72" t="n">
-        <v>2.142910417234192</v>
+        <v>2.123692246652389</v>
       </c>
       <c r="E72" t="n">
-        <v>2.58920927631929</v>
+        <v>2.577548156030716</v>
       </c>
       <c r="F72" t="n">
         <v>24</v>
@@ -2034,13 +2034,13 @@
         </is>
       </c>
       <c r="C73" t="n">
-        <v>2.531032083150182</v>
+        <v>2.548745989909999</v>
       </c>
       <c r="D73" t="n">
-        <v>1.299470853938846</v>
+        <v>1.308564417531557</v>
       </c>
       <c r="E73" t="n">
-        <v>1.738718860656065</v>
+        <v>1.744487648031357</v>
       </c>
       <c r="F73" t="n">
         <v>24</v>
@@ -2056,13 +2056,13 @@
         </is>
       </c>
       <c r="C74" t="n">
-        <v>5.584540487322622</v>
+        <v>5.58882029256189</v>
       </c>
       <c r="D74" t="n">
-        <v>1.751470831300917</v>
+        <v>1.751164216038132</v>
       </c>
       <c r="E74" t="n">
-        <v>5.138308545776261</v>
+        <v>5.155916087014879</v>
       </c>
       <c r="F74" t="n">
         <v>24</v>
@@ -2169,10 +2169,10 @@
         <v>2.132042248314101</v>
       </c>
       <c r="D79" t="n">
-        <v>0.6428229166666667</v>
+        <v>0.6428229166666665</v>
       </c>
       <c r="E79" t="n">
-        <v>0.8858431964212591</v>
+        <v>0.8858431964212589</v>
       </c>
       <c r="F79" t="n">
         <v>24</v>
@@ -2210,13 +2210,13 @@
         </is>
       </c>
       <c r="C81" t="n">
-        <v>11.95357191159133</v>
+        <v>11.95354597886902</v>
       </c>
       <c r="D81" t="n">
-        <v>2.695779166666667</v>
+        <v>2.695773180746039</v>
       </c>
       <c r="E81" t="n">
-        <v>5.699840079536589</v>
+        <v>5.699826858637452</v>
       </c>
       <c r="F81" t="n">
         <v>24</v>
@@ -2914,13 +2914,13 @@
         </is>
       </c>
       <c r="C113" t="n">
-        <v>1.070559794881523e-15</v>
+        <v>4.281589224803147e-15</v>
       </c>
       <c r="D113" t="n">
-        <v>1.1842378929335e-15</v>
+        <v>4.736951571734001e-15</v>
       </c>
       <c r="E113" t="n">
-        <v>4.102320397618269e-15</v>
+        <v>8.204640795236539e-15</v>
       </c>
       <c r="F113" t="n">
         <v>24</v>
@@ -3442,13 +3442,13 @@
         </is>
       </c>
       <c r="C137" t="n">
-        <v>0.1616672003448714</v>
+        <v>0.1616673181184397</v>
       </c>
       <c r="D137" t="n">
-        <v>0.1546900539378277</v>
+        <v>0.1546901666278592</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1930826935691561</v>
+        <v>0.1930827154329286</v>
       </c>
       <c r="F137" t="n">
         <v>24</v>
@@ -3464,13 +3464,13 @@
         </is>
       </c>
       <c r="C138" t="n">
-        <v>0.5093158282769115</v>
+        <v>0.5093158244451851</v>
       </c>
       <c r="D138" t="n">
-        <v>0.5188291649786461</v>
+        <v>0.5188291666666682</v>
       </c>
       <c r="E138" t="n">
-        <v>1.023310535885027</v>
+        <v>1.023311013918709</v>
       </c>
       <c r="F138" t="n">
         <v>24</v>
@@ -3486,13 +3486,13 @@
         </is>
       </c>
       <c r="C139" t="n">
-        <v>0.3316450970040485</v>
+        <v>0.331645097703351</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3362351659487721</v>
+        <v>0.3362351666666665</v>
       </c>
       <c r="E139" t="n">
-        <v>0.860705182266573</v>
+        <v>0.8607051828243312</v>
       </c>
       <c r="F139" t="n">
         <v>24</v>
@@ -3508,13 +3508,13 @@
         </is>
       </c>
       <c r="C140" t="n">
-        <v>5.23489436927471</v>
+        <v>5.234894364964473</v>
       </c>
       <c r="D140" t="n">
-        <v>4.128895505413309</v>
+        <v>4.128895499999997</v>
       </c>
       <c r="E140" t="n">
-        <v>10.72400509123193</v>
+        <v>10.72400509767724</v>
       </c>
       <c r="F140" t="n">
         <v>24</v>
@@ -3552,13 +3552,13 @@
         </is>
       </c>
       <c r="C142" t="n">
-        <v>0.2721455556442764</v>
+        <v>0.2721455409088561</v>
       </c>
       <c r="D142" t="n">
-        <v>0.2761700146295247</v>
+        <v>0.2761699999999993</v>
       </c>
       <c r="E142" t="n">
-        <v>0.58178147000375</v>
+        <v>0.5817814693026933</v>
       </c>
       <c r="F142" t="n">
         <v>24</v>
@@ -3574,13 +3574,13 @@
         </is>
       </c>
       <c r="C143" t="n">
-        <v>0.1367730807255171</v>
+        <v>0.1367731365584466</v>
       </c>
       <c r="D143" t="n">
-        <v>0.1360196112335714</v>
+        <v>0.1360196666666672</v>
       </c>
       <c r="E143" t="n">
-        <v>0.171503517674316</v>
+        <v>0.1715034856516531</v>
       </c>
       <c r="F143" t="n">
         <v>24</v>
@@ -3596,13 +3596,13 @@
         </is>
       </c>
       <c r="C144" t="n">
-        <v>0.144190731208956</v>
+        <v>0.1441912624749596</v>
       </c>
       <c r="D144" t="n">
-        <v>0.143806302692892</v>
+        <v>0.1438068333333315</v>
       </c>
       <c r="E144" t="n">
-        <v>0.1732807801187693</v>
+        <v>0.1732815232716211</v>
       </c>
       <c r="F144" t="n">
         <v>24</v>
@@ -3618,13 +3618,13 @@
         </is>
       </c>
       <c r="C145" t="n">
-        <v>0.2254913909667243</v>
+        <v>0.2254927758127508</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2306080968655273</v>
+        <v>0.2306094999999987</v>
       </c>
       <c r="E145" t="n">
-        <v>0.4798728878487774</v>
+        <v>0.479874813335727</v>
       </c>
       <c r="F145" t="n">
         <v>24</v>
@@ -3684,13 +3684,13 @@
         </is>
       </c>
       <c r="C148" t="n">
-        <v>0.1594039733961172</v>
+        <v>0.1594039737453103</v>
       </c>
       <c r="D148" t="n">
-        <v>0.1593678329840819</v>
+        <v>0.1593678333333279</v>
       </c>
       <c r="E148" t="n">
-        <v>0.2131774025263152</v>
+        <v>0.2131774026657862</v>
       </c>
       <c r="F148" t="n">
         <v>24</v>
@@ -3706,13 +3706,13 @@
         </is>
       </c>
       <c r="C149" t="n">
-        <v>0.8349602379141249</v>
+        <v>0.8349602405124374</v>
       </c>
       <c r="D149" t="n">
-        <v>0.8046874974000566</v>
+        <v>0.8046874999999988</v>
       </c>
       <c r="E149" t="n">
-        <v>2.393891815756223</v>
+        <v>2.393891816124388</v>
       </c>
       <c r="F149" t="n">
         <v>24</v>
@@ -3750,13 +3750,13 @@
         </is>
       </c>
       <c r="C151" t="n">
-        <v>0.8528202755817563</v>
+        <v>0.8528202755429297</v>
       </c>
       <c r="D151" t="n">
-        <v>0.8238901667054707</v>
+        <v>0.8238901666666655</v>
       </c>
       <c r="E151" t="n">
-        <v>2.359913035831876</v>
+        <v>2.359913035828646</v>
       </c>
       <c r="F151" t="n">
         <v>24</v>
@@ -3772,13 +3772,13 @@
         </is>
       </c>
       <c r="C152" t="n">
-        <v>0.8532938854484791</v>
+        <v>0.8532939046101001</v>
       </c>
       <c r="D152" t="n">
-        <v>0.8268276473417254</v>
+        <v>0.8268276666666688</v>
       </c>
       <c r="E152" t="n">
-        <v>2.425549554698716</v>
+        <v>2.425549557919607</v>
       </c>
       <c r="F152" t="n">
         <v>24</v>
@@ -3794,13 +3794,13 @@
         </is>
       </c>
       <c r="C153" t="n">
-        <v>0.1607558408614936</v>
+        <v>0.1607558407845217</v>
       </c>
       <c r="D153" t="n">
-        <v>0.1615000000776075</v>
+        <v>0.1614999999999972</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2037129095769427</v>
+        <v>0.2037129094845623</v>
       </c>
       <c r="F153" t="n">
         <v>24</v>
@@ -4080,13 +4080,13 @@
         </is>
       </c>
       <c r="C166" t="n">
-        <v>0.2226321946336907</v>
+        <v>0.222632194361445</v>
       </c>
       <c r="D166" t="n">
-        <v>0.2142000002619397</v>
+        <v>0.2142000000000053</v>
       </c>
       <c r="E166" t="n">
-        <v>0.2142000002619397</v>
+        <v>0.2142000000000053</v>
       </c>
       <c r="F166" t="n">
         <v>1</v>
@@ -4520,13 +4520,13 @@
         </is>
       </c>
       <c r="C186" t="n">
-        <v>0.318726428771532</v>
+        <v>0.3187264312007056</v>
       </c>
       <c r="D186" t="n">
-        <v>0.3016666643462423</v>
+        <v>0.3016666666666665</v>
       </c>
       <c r="E186" t="n">
-        <v>0.7672534731582349</v>
+        <v>0.7672534734362542</v>
       </c>
       <c r="F186" t="n">
         <v>24</v>
@@ -5246,13 +5246,13 @@
         </is>
       </c>
       <c r="C219" t="n">
-        <v>0.7343777834949795</v>
+        <v>0.7343777834656042</v>
       </c>
       <c r="D219" t="n">
-        <v>0.7990000000339533</v>
+        <v>0.7989999999999989</v>
       </c>
       <c r="E219" t="n">
-        <v>2.871676839023008</v>
+        <v>2.871676838974052</v>
       </c>
       <c r="F219" t="n">
         <v>24</v>
@@ -5268,13 +5268,13 @@
         </is>
       </c>
       <c r="C220" t="n">
-        <v>0.5360892862583295</v>
+        <v>0.5360892685024846</v>
       </c>
       <c r="D220" t="n">
-        <v>0.6100416857781786</v>
+        <v>0.6100416666666634</v>
       </c>
       <c r="E220" t="n">
-        <v>1.45174098807231</v>
+        <v>1.45174096289019</v>
       </c>
       <c r="F220" t="n">
         <v>24</v>
@@ -5290,13 +5290,13 @@
         </is>
       </c>
       <c r="C221" t="n">
-        <v>0.1557916673421748</v>
+        <v>0.1557916661921347</v>
       </c>
       <c r="D221" t="n">
-        <v>0.1835708346824128</v>
+        <v>0.183570833333329</v>
       </c>
       <c r="E221" t="n">
-        <v>0.2195595937258321</v>
+        <v>0.2195595923282149</v>
       </c>
       <c r="F221" t="n">
         <v>24</v>
@@ -5312,13 +5312,13 @@
         </is>
       </c>
       <c r="C222" t="n">
-        <v>1.314431076153655</v>
+        <v>1.314431075143556</v>
       </c>
       <c r="D222" t="n">
-        <v>1.502279167859924</v>
+        <v>1.502279166666667</v>
       </c>
       <c r="E222" t="n">
-        <v>3.241942712905654</v>
+        <v>3.241942713064444</v>
       </c>
       <c r="F222" t="n">
         <v>24</v>
@@ -5334,13 +5334,13 @@
         </is>
       </c>
       <c r="C223" t="n">
-        <v>1.169798519966277</v>
+        <v>1.169798519419066</v>
       </c>
       <c r="D223" t="n">
-        <v>1.128075000646954</v>
+        <v>1.128075</v>
       </c>
       <c r="E223" t="n">
-        <v>4.654734818820434</v>
+        <v>4.654734818798306</v>
       </c>
       <c r="F223" t="n">
         <v>24</v>
@@ -5378,13 +5378,13 @@
         </is>
       </c>
       <c r="C225" t="n">
-        <v>0.6315206889425561</v>
+        <v>0.6315206889328171</v>
       </c>
       <c r="D225" t="n">
-        <v>0.7073916666769714</v>
+        <v>0.7073916666666639</v>
       </c>
       <c r="E225" t="n">
-        <v>1.918466581522914</v>
+        <v>1.918466581456832</v>
       </c>
       <c r="F225" t="n">
         <v>24</v>
@@ -5400,13 +5400,13 @@
         </is>
       </c>
       <c r="C226" t="n">
-        <v>0.1849194530654629</v>
+        <v>0.184919333755449</v>
       </c>
       <c r="D226" t="n">
-        <v>0.1976376274299092</v>
+        <v>0.1976375000000002</v>
       </c>
       <c r="E226" t="n">
-        <v>0.2229593686954937</v>
+        <v>0.2229592479580068</v>
       </c>
       <c r="F226" t="n">
         <v>24</v>
@@ -5422,13 +5422,13 @@
         </is>
       </c>
       <c r="C227" t="n">
-        <v>0.800087968562165</v>
+        <v>0.8000884552045676</v>
       </c>
       <c r="D227" t="n">
-        <v>0.7652994943658141</v>
+        <v>0.7652999999999999</v>
       </c>
       <c r="E227" t="n">
-        <v>2.411142095062317</v>
+        <v>2.411142694519205</v>
       </c>
       <c r="F227" t="n">
         <v>24</v>
@@ -5444,13 +5444,13 @@
         </is>
       </c>
       <c r="C228" t="n">
-        <v>0.6189796969693926</v>
+        <v>0.6189796969800128</v>
       </c>
       <c r="D228" t="n">
-        <v>0.6425624999890852</v>
+        <v>0.6425624999999991</v>
       </c>
       <c r="E228" t="n">
-        <v>1.763918440420013</v>
+        <v>1.763918440456739</v>
       </c>
       <c r="F228" t="n">
         <v>24</v>
@@ -5466,13 +5466,13 @@
         </is>
       </c>
       <c r="C229" t="n">
-        <v>2.084153717492654</v>
+        <v>2.084153717522464</v>
       </c>
       <c r="D229" t="n">
-        <v>2.464458333299987</v>
+        <v>2.464458333333335</v>
       </c>
       <c r="E229" t="n">
-        <v>3.997438487100353</v>
+        <v>3.997438487123142</v>
       </c>
       <c r="F229" t="n">
         <v>24</v>
@@ -5554,13 +5554,13 @@
         </is>
       </c>
       <c r="C233" t="n">
-        <v>0.8525958856444252</v>
+        <v>0.8525958854689449</v>
       </c>
       <c r="D233" t="n">
-        <v>0.9414375002012972</v>
+        <v>0.9414374999999957</v>
       </c>
       <c r="E233" t="n">
-        <v>2.760816806147249</v>
+        <v>2.760816806143306</v>
       </c>
       <c r="F233" t="n">
         <v>24</v>
@@ -5576,13 +5576,13 @@
         </is>
       </c>
       <c r="C234" t="n">
-        <v>0.8333314910171438</v>
+        <v>0.8333314730663663</v>
       </c>
       <c r="D234" t="n">
-        <v>0.9208208539952309</v>
+        <v>0.9208208333333303</v>
       </c>
       <c r="E234" t="n">
-        <v>2.818953961391298</v>
+        <v>2.818953961356946</v>
       </c>
       <c r="F234" t="n">
         <v>24</v>
@@ -5598,13 +5598,13 @@
         </is>
       </c>
       <c r="C235" t="n">
-        <v>0.3582008949069125</v>
+        <v>0.3582008950629165</v>
       </c>
       <c r="D235" t="n">
-        <v>0.4263083331556796</v>
+        <v>0.4263083333333342</v>
       </c>
       <c r="E235" t="n">
-        <v>0.7821387572637651</v>
+        <v>0.7821387574039105</v>
       </c>
       <c r="F235" t="n">
         <v>24</v>
@@ -5620,13 +5620,13 @@
         </is>
       </c>
       <c r="C236" t="n">
-        <v>0.1877071313516359</v>
+        <v>0.1877071313607029</v>
       </c>
       <c r="D236" t="n">
-        <v>0.2253708333224242</v>
+        <v>0.2253708333333382</v>
       </c>
       <c r="E236" t="n">
-        <v>0.2664446276064717</v>
+        <v>0.2664446276120711</v>
       </c>
       <c r="F236" t="n">
         <v>24</v>
@@ -5642,13 +5642,13 @@
         </is>
       </c>
       <c r="C237" t="n">
-        <v>0.1321681172718895</v>
+        <v>0.1321681172336429</v>
       </c>
       <c r="D237" t="n">
-        <v>0.1586375000454693</v>
+        <v>0.1586374999999946</v>
       </c>
       <c r="E237" t="n">
-        <v>0.1884726009390559</v>
+        <v>0.1884726007938514</v>
       </c>
       <c r="F237" t="n">
         <v>24</v>
@@ -5664,13 +5664,13 @@
         </is>
       </c>
       <c r="C238" t="n">
-        <v>0.1480311969225024</v>
+        <v>0.1480311968562691</v>
       </c>
       <c r="D238" t="n">
-        <v>0.1775166667448792</v>
+        <v>0.1775166666666627</v>
       </c>
       <c r="E238" t="n">
-        <v>0.2167029069548247</v>
+        <v>0.2167029072255346</v>
       </c>
       <c r="F238" t="n">
         <v>24</v>
@@ -6522,13 +6522,13 @@
         </is>
       </c>
       <c r="C277" t="n">
-        <v>0.5015450152745771</v>
+        <v>0.5015450152745756</v>
       </c>
       <c r="D277" t="n">
-        <v>0.2053263333333361</v>
+        <v>0.2053263333333355</v>
       </c>
       <c r="E277" t="n">
-        <v>0.2776944181043887</v>
+        <v>0.2776944181043871</v>
       </c>
       <c r="F277" t="n">
         <v>24</v>
@@ -7116,13 +7116,13 @@
         </is>
       </c>
       <c r="C304" t="n">
-        <v>5.234639980161058</v>
+        <v>5.234639980458187</v>
       </c>
       <c r="D304" t="n">
-        <v>1.946540916550251</v>
+        <v>1.946540916666666</v>
       </c>
       <c r="E304" t="n">
-        <v>2.321791690767327</v>
+        <v>2.321791690833575</v>
       </c>
       <c r="F304" t="n">
         <v>24</v>
@@ -7138,13 +7138,13 @@
         </is>
       </c>
       <c r="C305" t="n">
-        <v>6.641633838884322</v>
+        <v>6.641633839351674</v>
       </c>
       <c r="D305" t="n">
-        <v>2.411558916511445</v>
+        <v>2.411558916666666</v>
       </c>
       <c r="E305" t="n">
-        <v>2.850138423688164</v>
+        <v>2.850138423952685</v>
       </c>
       <c r="F305" t="n">
         <v>24</v>
@@ -7160,13 +7160,13 @@
         </is>
       </c>
       <c r="C306" t="n">
-        <v>3.218382499337451</v>
+        <v>3.21838251591544</v>
       </c>
       <c r="D306" t="n">
-        <v>1.261867243752377</v>
+        <v>1.261867249999999</v>
       </c>
       <c r="E306" t="n">
-        <v>1.507016281848522</v>
+        <v>1.507016289318896</v>
       </c>
       <c r="F306" t="n">
         <v>24</v>
@@ -7182,13 +7182,13 @@
         </is>
       </c>
       <c r="C307" t="n">
-        <v>4.859069137293997</v>
+        <v>4.859069136519728</v>
       </c>
       <c r="D307" t="n">
-        <v>1.849863084109437</v>
+        <v>1.849863083333334</v>
       </c>
       <c r="E307" t="n">
-        <v>2.287245606503409</v>
+        <v>2.28724561092132</v>
       </c>
       <c r="F307" t="n">
         <v>24</v>
@@ -7226,13 +7226,13 @@
         </is>
       </c>
       <c r="C309" t="n">
-        <v>4.311746868869126</v>
+        <v>4.311746868545143</v>
       </c>
       <c r="D309" t="n">
-        <v>1.431618750116416</v>
+        <v>1.431618750000001</v>
       </c>
       <c r="E309" t="n">
-        <v>1.744705981437721</v>
+        <v>1.74470598134934</v>
       </c>
       <c r="F309" t="n">
         <v>24</v>
@@ -8326,13 +8326,13 @@
         </is>
       </c>
       <c r="C359" t="n">
-        <v>0.5241573763548238</v>
+        <v>0.5241573763548254</v>
       </c>
       <c r="D359" t="n">
-        <v>0.833317999999989</v>
+        <v>0.8333179999999913</v>
       </c>
       <c r="E359" t="n">
-        <v>0.833317999999989</v>
+        <v>0.8333179999999912</v>
       </c>
       <c r="F359" t="n">
         <v>24</v>
@@ -8876,13 +8876,13 @@
         </is>
       </c>
       <c r="C384" t="n">
-        <v>0.7317911419286013</v>
+        <v>0.7317911419409108</v>
       </c>
       <c r="D384" t="n">
-        <v>1.116037499980582</v>
+        <v>1.116037499999984</v>
       </c>
       <c r="E384" t="n">
-        <v>2.314292209409686</v>
+        <v>2.314292209474269</v>
       </c>
       <c r="F384" t="n">
         <v>24</v>
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="C390" t="n">
-        <v>1.919844574352221</v>
+        <v>1.919844578018533</v>
       </c>
       <c r="D390" t="n">
-        <v>2.625299994800111</v>
+        <v>2.625299999999996</v>
       </c>
       <c r="E390" t="n">
-        <v>4.017133894976592</v>
+        <v>4.017133894773941</v>
       </c>
       <c r="F390" t="n">
         <v>24</v>
@@ -9030,13 +9030,13 @@
         </is>
       </c>
       <c r="C391" t="n">
-        <v>3.277495849893832</v>
+        <v>3.277495850817811</v>
       </c>
       <c r="D391" t="n">
-        <v>4.339062498554511</v>
+        <v>4.339062500000002</v>
       </c>
       <c r="E391" t="n">
-        <v>6.663135472368761</v>
+        <v>6.663135469569363</v>
       </c>
       <c r="F391" t="n">
         <v>24</v>
@@ -9514,13 +9514,13 @@
         </is>
       </c>
       <c r="C413" t="n">
-        <v>8.332405807816681</v>
+        <v>8.332405807643644</v>
       </c>
       <c r="D413" t="n">
-        <v>2.786198500048506</v>
+        <v>2.7861985</v>
       </c>
       <c r="E413" t="n">
-        <v>4.153346158554852</v>
+        <v>4.153346158519336</v>
       </c>
       <c r="F413" t="n">
         <v>24</v>
@@ -9536,13 +9536,13 @@
         </is>
       </c>
       <c r="C414" t="n">
-        <v>4.818989126662167</v>
+        <v>4.81898912641828</v>
       </c>
       <c r="D414" t="n">
-        <v>1.691173500067908</v>
+        <v>1.691173499999999</v>
       </c>
       <c r="E414" t="n">
-        <v>3.728841475332781</v>
+        <v>3.728841475327244</v>
       </c>
       <c r="F414" t="n">
         <v>24</v>
@@ -9558,13 +9558,13 @@
         </is>
       </c>
       <c r="C415" t="n">
-        <v>3.472039361949539</v>
+        <v>3.472039362090741</v>
       </c>
       <c r="D415" t="n">
-        <v>1.31095266661816</v>
+        <v>1.310952666666666</v>
       </c>
       <c r="E415" t="n">
-        <v>1.670340369918788</v>
+        <v>1.67034036993582</v>
       </c>
       <c r="F415" t="n">
         <v>24</v>
@@ -9580,13 +9580,13 @@
         </is>
       </c>
       <c r="C416" t="n">
-        <v>4.189859337215793</v>
+        <v>4.189859337330124</v>
       </c>
       <c r="D416" t="n">
-        <v>1.616913999951492</v>
+        <v>1.616913999999998</v>
       </c>
       <c r="E416" t="n">
-        <v>1.94393994697954</v>
+        <v>1.943939947015852</v>
       </c>
       <c r="F416" t="n">
         <v>24</v>
@@ -9602,13 +9602,13 @@
         </is>
       </c>
       <c r="C417" t="n">
-        <v>2.884615198353337</v>
+        <v>2.884615198172631</v>
       </c>
       <c r="D417" t="n">
-        <v>1.166593166734575</v>
+        <v>1.166593166666667</v>
       </c>
       <c r="E417" t="n">
-        <v>1.719658062134797</v>
+        <v>1.719658062121846</v>
       </c>
       <c r="F417" t="n">
         <v>24</v>
@@ -9624,13 +9624,13 @@
         </is>
       </c>
       <c r="C418" t="n">
-        <v>4.907119407048857</v>
+        <v>4.907119407171583</v>
       </c>
       <c r="D418" t="n">
-        <v>1.40855266661816</v>
+        <v>1.408552666666666</v>
       </c>
       <c r="E418" t="n">
-        <v>3.400089190058242</v>
+        <v>3.400089190067273</v>
       </c>
       <c r="F418" t="n">
         <v>24</v>
@@ -9646,13 +9646,13 @@
         </is>
       </c>
       <c r="C419" t="n">
-        <v>6.313917504547238</v>
+        <v>6.313917504437129</v>
       </c>
       <c r="D419" t="n">
-        <v>2.340705666715173</v>
+        <v>2.340705666666667</v>
       </c>
       <c r="E419" t="n">
-        <v>4.358624756004057</v>
+        <v>4.358624756002441</v>
       </c>
       <c r="F419" t="n">
         <v>24</v>
@@ -9668,13 +9668,13 @@
         </is>
       </c>
       <c r="C420" t="n">
-        <v>3.495355528001558</v>
+        <v>3.495355527881046</v>
       </c>
       <c r="D420" t="n">
-        <v>1.398602666715173</v>
+        <v>1.398602666666667</v>
       </c>
       <c r="E420" t="n">
-        <v>1.702893937656501</v>
+        <v>1.702893937596819</v>
       </c>
       <c r="F420" t="n">
         <v>24</v>
@@ -9690,13 +9690,13 @@
         </is>
       </c>
       <c r="C421" t="n">
-        <v>1.919490026958591</v>
+        <v>1.919490027089136</v>
       </c>
       <c r="D421" t="n">
-        <v>0.7415609999514921</v>
+        <v>0.7415609999999985</v>
       </c>
       <c r="E421" t="n">
-        <v>1.149653162277253</v>
+        <v>1.149653162275038</v>
       </c>
       <c r="F421" t="n">
         <v>24</v>
@@ -9712,13 +9712,13 @@
         </is>
       </c>
       <c r="C422" t="n">
-        <v>4.474893599565042</v>
+        <v>4.474893599698813</v>
       </c>
       <c r="D422" t="n">
-        <v>1.716015166618162</v>
+        <v>1.716015166666669</v>
       </c>
       <c r="E422" t="n">
-        <v>2.180715000131541</v>
+        <v>2.180715000121292</v>
       </c>
       <c r="F422" t="n">
         <v>24</v>
@@ -9734,13 +9734,13 @@
         </is>
       </c>
       <c r="C423" t="n">
-        <v>2.266716968268949</v>
+        <v>2.26671696843887</v>
       </c>
       <c r="D423" t="n">
-        <v>0.9229568332654227</v>
+        <v>0.9229568333333317</v>
       </c>
       <c r="E423" t="n">
-        <v>1.144409993113425</v>
+        <v>1.144409993135034</v>
       </c>
       <c r="F423" t="n">
         <v>24</v>
@@ -9756,13 +9756,13 @@
         </is>
       </c>
       <c r="C424" t="n">
-        <v>5.285337102928081</v>
+        <v>5.285337103050578</v>
       </c>
       <c r="D424" t="n">
-        <v>1.915126499951494</v>
+        <v>1.915126500000001</v>
       </c>
       <c r="E424" t="n">
-        <v>2.639357892476227</v>
+        <v>2.639357892516158</v>
       </c>
       <c r="F424" t="n">
         <v>24</v>
@@ -9778,13 +9778,13 @@
         </is>
       </c>
       <c r="C425" t="n">
-        <v>4.665901728412342</v>
+        <v>4.665901728565737</v>
       </c>
       <c r="D425" t="n">
-        <v>1.827360999951493</v>
+        <v>1.827361</v>
       </c>
       <c r="E425" t="n">
-        <v>2.440167946112838</v>
+        <v>2.440167946210329</v>
       </c>
       <c r="F425" t="n">
         <v>24</v>
@@ -9800,13 +9800,13 @@
         </is>
       </c>
       <c r="C426" t="n">
-        <v>9.565568335097668</v>
+        <v>9.565568335316103</v>
       </c>
       <c r="D426" t="n">
-        <v>3.034184833284826</v>
+        <v>3.034184833333332</v>
       </c>
       <c r="E426" t="n">
-        <v>4.645096597649687</v>
+        <v>4.645096597767083</v>
       </c>
       <c r="F426" t="n">
         <v>24</v>
@@ -9822,13 +9822,13 @@
         </is>
       </c>
       <c r="C427" t="n">
-        <v>2.073694630349789</v>
+        <v>2.073694630505337</v>
       </c>
       <c r="D427" t="n">
-        <v>0.854106833265423</v>
+        <v>0.8541068333333319</v>
       </c>
       <c r="E427" t="n">
-        <v>1.340296650601615</v>
+        <v>1.340296650616571</v>
       </c>
       <c r="F427" t="n">
         <v>24</v>
@@ -9844,13 +9844,13 @@
         </is>
       </c>
       <c r="C428" t="n">
-        <v>3.532087982329404</v>
+        <v>3.532087982167264</v>
       </c>
       <c r="D428" t="n">
-        <v>1.390731833401242</v>
+        <v>1.390731833333333</v>
       </c>
       <c r="E428" t="n">
-        <v>1.820504914606152</v>
+        <v>1.820504914564638</v>
       </c>
       <c r="F428" t="n">
         <v>24</v>
@@ -9866,13 +9866,13 @@
         </is>
       </c>
       <c r="C429" t="n">
-        <v>3.541279553861334</v>
+        <v>3.541279553678601</v>
       </c>
       <c r="D429" t="n">
-        <v>1.242051500067909</v>
+        <v>1.2420515</v>
       </c>
       <c r="E429" t="n">
-        <v>2.286549513596788</v>
+        <v>2.286549513572943</v>
       </c>
       <c r="F429" t="n">
         <v>24</v>
@@ -9888,13 +9888,13 @@
         </is>
       </c>
       <c r="C430" t="n">
-        <v>5.407393032880956</v>
+        <v>5.407393033003348</v>
       </c>
       <c r="D430" t="n">
-        <v>1.879426499951491</v>
+        <v>1.879426499999997</v>
       </c>
       <c r="E430" t="n">
-        <v>2.317456363069046</v>
+        <v>2.317456363081584</v>
       </c>
       <c r="F430" t="n">
         <v>24</v>
@@ -9910,13 +9910,13 @@
         </is>
       </c>
       <c r="C431" t="n">
-        <v>4.278922459852308</v>
+        <v>4.278922459726082</v>
       </c>
       <c r="D431" t="n">
-        <v>1.53134433338184</v>
+        <v>1.531344333333334</v>
       </c>
       <c r="E431" t="n">
-        <v>1.902711802170522</v>
+        <v>1.902711802157823</v>
       </c>
       <c r="F431" t="n">
         <v>24</v>
@@ -9932,13 +9932,13 @@
         </is>
       </c>
       <c r="C432" t="n">
-        <v>4.363261800665043</v>
+        <v>4.363261800551963</v>
       </c>
       <c r="D432" t="n">
-        <v>1.571515166715175</v>
+        <v>1.571515166666668</v>
       </c>
       <c r="E432" t="n">
-        <v>2.202746314731267</v>
+        <v>2.202746314638615</v>
       </c>
       <c r="F432" t="n">
         <v>24</v>
@@ -9954,13 +9954,13 @@
         </is>
       </c>
       <c r="C433" t="n">
-        <v>10.7349048945132</v>
+        <v>10.73490489473637</v>
       </c>
       <c r="D433" t="n">
-        <v>3.587244333265426</v>
+        <v>3.587244333333335</v>
       </c>
       <c r="E433" t="n">
-        <v>5.245633036543216</v>
+        <v>5.245633036679559</v>
       </c>
       <c r="F433" t="n">
         <v>24</v>
@@ -9976,13 +9976,13 @@
         </is>
       </c>
       <c r="C434" t="n">
-        <v>3.477227656598673</v>
+        <v>3.477227656382848</v>
       </c>
       <c r="D434" t="n">
-        <v>1.253051500067907</v>
+        <v>1.253051499999998</v>
       </c>
       <c r="E434" t="n">
-        <v>1.773249803592247</v>
+        <v>1.773249803558615</v>
       </c>
       <c r="F434" t="n">
         <v>24</v>
@@ -9998,13 +9998,13 @@
         </is>
       </c>
       <c r="C435" t="n">
-        <v>4.049220646438406</v>
+        <v>4.049220646318574</v>
       </c>
       <c r="D435" t="n">
-        <v>1.391659833381841</v>
+        <v>1.391659833333334</v>
       </c>
       <c r="E435" t="n">
-        <v>2.007818795244855</v>
+        <v>2.007818795223812</v>
       </c>
       <c r="F435" t="n">
         <v>24</v>
@@ -10020,13 +10020,13 @@
         </is>
       </c>
       <c r="C436" t="n">
-        <v>3.679822638308769</v>
+        <v>3.679822638118146</v>
       </c>
       <c r="D436" t="n">
-        <v>1.167080666734573</v>
+        <v>1.167080666666664</v>
       </c>
       <c r="E436" t="n">
-        <v>1.657416894311552</v>
+        <v>1.65741689424759</v>
       </c>
       <c r="F436" t="n">
         <v>24</v>
@@ -10042,13 +10042,13 @@
         </is>
       </c>
       <c r="C437" t="n">
-        <v>1.995523002432673</v>
+        <v>1.995523002591016</v>
       </c>
       <c r="D437" t="n">
-        <v>0.6223443332848239</v>
+        <v>0.6223443333333303</v>
       </c>
       <c r="E437" t="n">
-        <v>0.8541637364398154</v>
+        <v>0.8541637364330849</v>
       </c>
       <c r="F437" t="n">
         <v>24</v>
@@ -10064,13 +10064,13 @@
         </is>
       </c>
       <c r="C438" t="n">
-        <v>3.935828300311744</v>
+        <v>3.935828300446635</v>
       </c>
       <c r="D438" t="n">
-        <v>1.231468166618161</v>
+        <v>1.231468166666668</v>
       </c>
       <c r="E438" t="n">
-        <v>1.723573638750736</v>
+        <v>1.72357363881578</v>
       </c>
       <c r="F438" t="n">
         <v>24</v>
@@ -10086,13 +10086,13 @@
         </is>
       </c>
       <c r="C439" t="n">
-        <v>6.011095850174889</v>
+        <v>6.011095850039446</v>
       </c>
       <c r="D439" t="n">
-        <v>1.619680666715173</v>
+        <v>1.619680666666666</v>
       </c>
       <c r="E439" t="n">
-        <v>3.016651181578942</v>
+        <v>3.016651181548395</v>
       </c>
       <c r="F439" t="n">
         <v>24</v>
@@ -10108,13 +10108,13 @@
         </is>
       </c>
       <c r="C440" t="n">
-        <v>4.838777927672714</v>
+        <v>4.838777927850709</v>
       </c>
       <c r="D440" t="n">
-        <v>1.496987499951494</v>
+        <v>1.496987500000001</v>
       </c>
       <c r="E440" t="n">
-        <v>1.864371554343616</v>
+        <v>1.864371554382692</v>
       </c>
       <c r="F440" t="n">
         <v>24</v>
@@ -10130,13 +10130,13 @@
         </is>
       </c>
       <c r="C441" t="n">
-        <v>0.4813310663171816</v>
+        <v>0.4813310661102579</v>
       </c>
       <c r="D441" t="n">
-        <v>0.1602756667345767</v>
+        <v>0.1602756666666677</v>
       </c>
       <c r="E441" t="n">
-        <v>0.184918918487121</v>
+        <v>0.1849189184264301</v>
       </c>
       <c r="F441" t="n">
         <v>24</v>
@@ -10152,13 +10152,13 @@
         </is>
       </c>
       <c r="C442" t="n">
-        <v>1.879974967748105</v>
+        <v>1.879974967550955</v>
       </c>
       <c r="D442" t="n">
-        <v>0.654923500067909</v>
+        <v>0.6549235000000001</v>
       </c>
       <c r="E442" t="n">
-        <v>0.8023056084116733</v>
+        <v>0.8023056083276501</v>
       </c>
       <c r="F442" t="n">
         <v>24</v>
@@ -10174,13 +10174,13 @@
         </is>
       </c>
       <c r="C443" t="n">
-        <v>3.197555769151379</v>
+        <v>3.197555769357877</v>
       </c>
       <c r="D443" t="n">
-        <v>1.080702666598759</v>
+        <v>1.080702666666667</v>
       </c>
       <c r="E443" t="n">
-        <v>1.448749669875562</v>
+        <v>1.448749669900682</v>
       </c>
       <c r="F443" t="n">
         <v>24</v>
@@ -10196,13 +10196,13 @@
         </is>
       </c>
       <c r="C444" t="n">
-        <v>2.392211591645351</v>
+        <v>2.39221159146919</v>
       </c>
       <c r="D444" t="n">
-        <v>0.8333276667345758</v>
+        <v>0.8333276666666669</v>
       </c>
       <c r="E444" t="n">
-        <v>1.405454865480567</v>
+        <v>1.405454865421631</v>
       </c>
       <c r="F444" t="n">
         <v>24</v>
@@ -10218,13 +10218,13 @@
         </is>
       </c>
       <c r="C445" t="n">
-        <v>3.653695962409612</v>
+        <v>3.653695962599603</v>
       </c>
       <c r="D445" t="n">
-        <v>1.193151499932091</v>
+        <v>1.1931515</v>
       </c>
       <c r="E445" t="n">
-        <v>1.486351352281897</v>
+        <v>1.486351352301109</v>
       </c>
       <c r="F445" t="n">
         <v>24</v>
@@ -10240,13 +10240,13 @@
         </is>
       </c>
       <c r="C446" t="n">
-        <v>3.835476814185295</v>
+        <v>3.835476814007629</v>
       </c>
       <c r="D446" t="n">
-        <v>1.362855666734576</v>
+        <v>1.362855666666667</v>
       </c>
       <c r="E446" t="n">
-        <v>1.771933249393902</v>
+        <v>1.771933249364659</v>
       </c>
       <c r="F446" t="n">
         <v>24</v>
@@ -10262,13 +10262,13 @@
         </is>
       </c>
       <c r="C447" t="n">
-        <v>4.098606433561438</v>
+        <v>4.09860643342578</v>
       </c>
       <c r="D447" t="n">
-        <v>1.34938483338184</v>
+        <v>1.349384833333333</v>
       </c>
       <c r="E447" t="n">
-        <v>2.036688047198838</v>
+        <v>2.036688047186903</v>
       </c>
       <c r="F447" t="n">
         <v>24</v>
@@ -10284,13 +10284,13 @@
         </is>
       </c>
       <c r="C448" t="n">
-        <v>3.852115530907606</v>
+        <v>3.852115531102231</v>
       </c>
       <c r="D448" t="n">
-        <v>1.264351499932091</v>
+        <v>1.2643515</v>
       </c>
       <c r="E448" t="n">
-        <v>1.753393231253943</v>
+        <v>1.753393231257799</v>
       </c>
       <c r="F448" t="n">
         <v>24</v>
@@ -10306,13 +10306,13 @@
         </is>
       </c>
       <c r="C449" t="n">
-        <v>3.244906410973087</v>
+        <v>3.244906410750523</v>
       </c>
       <c r="D449" t="n">
-        <v>0.9295526667345761</v>
+        <v>0.9295526666666672</v>
       </c>
       <c r="E449" t="n">
-        <v>1.333315114423019</v>
+        <v>1.333315114393692</v>
       </c>
       <c r="F449" t="n">
         <v>24</v>
@@ -10328,13 +10328,13 @@
         </is>
       </c>
       <c r="C450" t="n">
-        <v>2.866398638529292</v>
+        <v>2.866398638309732</v>
       </c>
       <c r="D450" t="n">
-        <v>1.033381833401245</v>
+        <v>1.033381833333336</v>
       </c>
       <c r="E450" t="n">
-        <v>1.534965095153812</v>
+        <v>1.534965095114763</v>
       </c>
       <c r="F450" t="n">
         <v>24</v>
@@ -10350,13 +10350,13 @@
         </is>
       </c>
       <c r="C451" t="n">
-        <v>4.607689161443712</v>
+        <v>4.607689161564482</v>
       </c>
       <c r="D451" t="n">
-        <v>1.65736516661816</v>
+        <v>1.657365166666666</v>
       </c>
       <c r="E451" t="n">
-        <v>2.102815341804531</v>
+        <v>2.102815341810592</v>
       </c>
       <c r="F451" t="n">
         <v>24</v>
@@ -10372,13 +10372,13 @@
         </is>
       </c>
       <c r="C452" t="n">
-        <v>5.909890723288384</v>
+        <v>5.909890723507552</v>
       </c>
       <c r="D452" t="n">
-        <v>2.090888999932089</v>
+        <v>2.090888999999998</v>
       </c>
       <c r="E452" t="n">
-        <v>2.655807580116733</v>
+        <v>2.65580758017293</v>
       </c>
       <c r="F452" t="n">
         <v>24</v>
@@ -10394,13 +10394,13 @@
         </is>
       </c>
       <c r="C453" t="n">
-        <v>3.667787839169892</v>
+        <v>3.667787839390206</v>
       </c>
       <c r="D453" t="n">
-        <v>1.218240166598758</v>
+        <v>1.218240166666667</v>
       </c>
       <c r="E453" t="n">
-        <v>1.441653101152841</v>
+        <v>1.441653101184192</v>
       </c>
       <c r="F453" t="n">
         <v>24</v>
@@ -10416,13 +10416,13 @@
         </is>
       </c>
       <c r="C454" t="n">
-        <v>3.15411170379914</v>
+        <v>3.15411170396985</v>
       </c>
       <c r="D454" t="n">
-        <v>1.219293166598759</v>
+        <v>1.219293166666668</v>
       </c>
       <c r="E454" t="n">
-        <v>1.7427385570109</v>
+        <v>1.742738557076382</v>
       </c>
       <c r="F454" t="n">
         <v>24</v>
@@ -10438,13 +10438,13 @@
         </is>
       </c>
       <c r="C455" t="n">
-        <v>2.33012575743412</v>
+        <v>2.330125757308818</v>
       </c>
       <c r="D455" t="n">
-        <v>0.842822333381838</v>
+        <v>0.8428223333333316</v>
       </c>
       <c r="E455" t="n">
-        <v>1.093175960867432</v>
+        <v>1.093175960830336</v>
       </c>
       <c r="F455" t="n">
         <v>24</v>
@@ -10460,13 +10460,13 @@
         </is>
       </c>
       <c r="C456" t="n">
-        <v>2.394723830585419</v>
+        <v>2.394723830774975</v>
       </c>
       <c r="D456" t="n">
-        <v>0.8294556665987574</v>
+        <v>0.8294556666666663</v>
       </c>
       <c r="E456" t="n">
-        <v>1.01891248167361</v>
+        <v>1.018912481768674</v>
       </c>
       <c r="F456" t="n">
         <v>24</v>
@@ -10482,13 +10482,13 @@
         </is>
       </c>
       <c r="C457" t="n">
-        <v>2.546832096358876</v>
+        <v>2.546832096148964</v>
       </c>
       <c r="D457" t="n">
-        <v>0.8508098334012422</v>
+        <v>0.8508098333333333</v>
       </c>
       <c r="E457" t="n">
-        <v>1.117752949822269</v>
+        <v>1.117752949740684</v>
       </c>
       <c r="F457" t="n">
         <v>24</v>
@@ -10504,13 +10504,13 @@
         </is>
       </c>
       <c r="C458" t="n">
-        <v>1.398858083493869</v>
+        <v>1.398858083696732</v>
       </c>
       <c r="D458" t="n">
-        <v>0.4638651665987578</v>
+        <v>0.4638651666666667</v>
       </c>
       <c r="E458" t="n">
-        <v>0.5655263153099439</v>
+        <v>0.5655263153211062</v>
       </c>
       <c r="F458" t="n">
         <v>24</v>
@@ -10526,13 +10526,13 @@
         </is>
       </c>
       <c r="C459" t="n">
-        <v>3.565576719239936</v>
+        <v>3.565576719036668</v>
       </c>
       <c r="D459" t="n">
-        <v>1.18411100006791</v>
+        <v>1.184111000000001</v>
       </c>
       <c r="E459" t="n">
-        <v>1.709666257053262</v>
+        <v>1.709666257023282</v>
       </c>
       <c r="F459" t="n">
         <v>24</v>
@@ -10548,13 +10548,13 @@
         </is>
       </c>
       <c r="C460" t="n">
-        <v>2.826016679838683</v>
+        <v>2.826016679682439</v>
       </c>
       <c r="D460" t="n">
-        <v>0.9445568333818368</v>
+        <v>0.9445568333333304</v>
       </c>
       <c r="E460" t="n">
-        <v>1.22072540459115</v>
+        <v>1.220725404552826</v>
       </c>
       <c r="F460" t="n">
         <v>24</v>
@@ -10570,13 +10570,13 @@
         </is>
       </c>
       <c r="C461" t="n">
-        <v>3.167805046892507</v>
+        <v>3.167805046675909</v>
       </c>
       <c r="D461" t="n">
-        <v>1.048015166734576</v>
+        <v>1.048015166666667</v>
       </c>
       <c r="E461" t="n">
-        <v>1.358001128166026</v>
+        <v>1.358001128149016</v>
       </c>
       <c r="F461" t="n">
         <v>24</v>
@@ -10592,13 +10592,13 @@
         </is>
       </c>
       <c r="C462" t="n">
-        <v>2.272879694844494</v>
+        <v>2.272879694709169</v>
       </c>
       <c r="D462" t="n">
-        <v>0.7581098333818401</v>
+        <v>0.7581098333333337</v>
       </c>
       <c r="E462" t="n">
-        <v>0.9444661355209222</v>
+        <v>0.9444661354546635</v>
       </c>
       <c r="F462" t="n">
         <v>24</v>
@@ -10614,13 +10614,13 @@
         </is>
       </c>
       <c r="C463" t="n">
-        <v>1.301411830476475</v>
+        <v>1.301411830272336</v>
       </c>
       <c r="D463" t="n">
-        <v>0.4341235000679082</v>
+        <v>0.4341234999999992</v>
       </c>
       <c r="E463" t="n">
-        <v>0.5303292334971917</v>
+        <v>0.5303292334207731</v>
       </c>
       <c r="F463" t="n">
         <v>24</v>
@@ -10636,13 +10636,13 @@
         </is>
       </c>
       <c r="C464" t="n">
-        <v>6.966582912092052</v>
+        <v>6.966582911945658</v>
       </c>
       <c r="D464" t="n">
-        <v>2.150626500048506</v>
+        <v>2.1506265</v>
       </c>
       <c r="E464" t="n">
-        <v>3.414584701711201</v>
+        <v>3.41458470171518</v>
       </c>
       <c r="F464" t="n">
         <v>24</v>
@@ -10658,13 +10658,13 @@
         </is>
       </c>
       <c r="C465" t="n">
-        <v>6.43174101067472</v>
+        <v>6.431741010822449</v>
       </c>
       <c r="D465" t="n">
-        <v>2.042530666618159</v>
+        <v>2.042530666666666</v>
       </c>
       <c r="E465" t="n">
-        <v>3.06453794669071</v>
+        <v>3.064537946701044</v>
       </c>
       <c r="F465" t="n">
         <v>24</v>
@@ -10680,13 +10680,13 @@
         </is>
       </c>
       <c r="C466" t="n">
-        <v>2.926672083091053</v>
+        <v>2.926672083524162</v>
       </c>
       <c r="D466" t="n">
-        <v>0.90860983322662</v>
+        <v>0.9086098333333341</v>
       </c>
       <c r="E466" t="n">
-        <v>1.79821383918292</v>
+        <v>1.798213839245488</v>
       </c>
       <c r="F466" t="n">
         <v>24</v>
@@ -10702,13 +10702,13 @@
         </is>
       </c>
       <c r="C467" t="n">
-        <v>1.683658855606921</v>
+        <v>1.683658855230445</v>
       </c>
       <c r="D467" t="n">
-        <v>0.5314693334449</v>
+        <v>0.5314693333333352</v>
       </c>
       <c r="E467" t="n">
-        <v>0.9737900138771225</v>
+        <v>0.9737900139333791</v>
       </c>
       <c r="F467" t="n">
         <v>24</v>
@@ -10724,13 +10724,13 @@
         </is>
       </c>
       <c r="C468" t="n">
-        <v>4.338190217647536</v>
+        <v>4.338190218746215</v>
       </c>
       <c r="D468" t="n">
-        <v>1.389605666317421</v>
+        <v>1.389605666666667</v>
       </c>
       <c r="E468" t="n">
-        <v>1.874587230937613</v>
+        <v>1.874587231534858</v>
       </c>
       <c r="F468" t="n">
         <v>24</v>
@@ -10746,13 +10746,13 @@
         </is>
       </c>
       <c r="C469" t="n">
-        <v>6.411196364197774</v>
+        <v>6.411196365463272</v>
       </c>
       <c r="D469" t="n">
-        <v>1.924205666264064</v>
+        <v>1.924205666661816</v>
       </c>
       <c r="E469" t="n">
-        <v>2.598232673695664</v>
+        <v>2.598232673950559</v>
       </c>
       <c r="F469" t="n">
         <v>24</v>
@@ -10768,13 +10768,13 @@
         </is>
       </c>
       <c r="C470" t="n">
-        <v>7.96556158775234</v>
+        <v>7.965561587968745</v>
       </c>
       <c r="D470" t="n">
-        <v>2.579559833250871</v>
+        <v>2.579559833328481</v>
       </c>
       <c r="E470" t="n">
-        <v>3.506443103161425</v>
+        <v>3.506443103177303</v>
       </c>
       <c r="F470" t="n">
         <v>24</v>
@@ -10790,13 +10790,13 @@
         </is>
       </c>
       <c r="C471" t="n">
-        <v>4.308410471285551</v>
+        <v>4.308410471143487</v>
       </c>
       <c r="D471" t="n">
-        <v>1.422968166715173</v>
+        <v>1.422968166666667</v>
       </c>
       <c r="E471" t="n">
-        <v>1.702114537206764</v>
+        <v>1.702114537152931</v>
       </c>
       <c r="F471" t="n">
         <v>24</v>
@@ -10812,13 +10812,13 @@
         </is>
       </c>
       <c r="C472" t="n">
-        <v>5.582058661460367</v>
+        <v>5.582058834822639</v>
       </c>
       <c r="D472" t="n">
-        <v>1.62478594916531</v>
+        <v>1.624786</v>
       </c>
       <c r="E472" t="n">
-        <v>2.325597978487642</v>
+        <v>2.325597992159723</v>
       </c>
       <c r="F472" t="n">
         <v>24</v>
@@ -10834,13 +10834,13 @@
         </is>
       </c>
       <c r="C473" t="n">
-        <v>5.355644342799353</v>
+        <v>5.355644305501336</v>
       </c>
       <c r="D473" t="n">
-        <v>1.526273512330321</v>
+        <v>1.526273499999999</v>
       </c>
       <c r="E473" t="n">
-        <v>1.902286383706574</v>
+        <v>1.902286383755259</v>
       </c>
       <c r="F473" t="n">
         <v>24</v>
@@ -10856,13 +10856,13 @@
         </is>
       </c>
       <c r="C474" t="n">
-        <v>4.605302920747995</v>
+        <v>4.605302920542977</v>
       </c>
       <c r="D474" t="n">
-        <v>1.502281833401244</v>
+        <v>1.502281833333335</v>
       </c>
       <c r="E474" t="n">
-        <v>2.059493313830785</v>
+        <v>2.059493313824383</v>
       </c>
       <c r="F474" t="n">
         <v>24</v>
@@ -10878,13 +10878,13 @@
         </is>
       </c>
       <c r="C475" t="n">
-        <v>5.845441691725569</v>
+        <v>5.845441691496777</v>
       </c>
       <c r="D475" t="n">
-        <v>1.957523500067909</v>
+        <v>1.9575235</v>
       </c>
       <c r="E475" t="n">
-        <v>2.676831415607663</v>
+        <v>2.676831415570905</v>
       </c>
       <c r="F475" t="n">
         <v>24</v>
@@ -10900,13 +10900,13 @@
         </is>
       </c>
       <c r="C476" t="n">
-        <v>3.612068117676907</v>
+        <v>3.612068117813503</v>
       </c>
       <c r="D476" t="n">
-        <v>1.185076499951493</v>
+        <v>1.1850765</v>
       </c>
       <c r="E476" t="n">
-        <v>1.536484021683894</v>
+        <v>1.536484021769832</v>
       </c>
       <c r="F476" t="n">
         <v>24</v>
@@ -10922,13 +10922,13 @@
         </is>
       </c>
       <c r="C477" t="n">
-        <v>3.78077014658716</v>
+        <v>3.780770146819644</v>
       </c>
       <c r="D477" t="n">
-        <v>1.160738999932091</v>
+        <v>1.160739</v>
       </c>
       <c r="E477" t="n">
-        <v>1.495011483819496</v>
+        <v>1.495011483926014</v>
       </c>
       <c r="F477" t="n">
         <v>24</v>
@@ -10944,13 +10944,13 @@
         </is>
       </c>
       <c r="C478" t="n">
-        <v>2.948961975491543</v>
+        <v>2.948961975708889</v>
       </c>
       <c r="D478" t="n">
-        <v>0.9610848332654243</v>
+        <v>0.9610848333333332</v>
       </c>
       <c r="E478" t="n">
-        <v>1.416457948228461</v>
+        <v>1.41645794824767</v>
       </c>
       <c r="F478" t="n">
         <v>24</v>
@@ -10966,13 +10966,13 @@
         </is>
       </c>
       <c r="C479" t="n">
-        <v>4.138208715906603</v>
+        <v>4.138208716068408</v>
       </c>
       <c r="D479" t="n">
-        <v>1.276027666618162</v>
+        <v>1.276027666666668</v>
       </c>
       <c r="E479" t="n">
-        <v>1.61947944753192</v>
+        <v>1.619479447611898</v>
       </c>
       <c r="F479" t="n">
         <v>24</v>
@@ -10988,13 +10988,13 @@
         </is>
       </c>
       <c r="C480" t="n">
-        <v>1.816825204480994</v>
+        <v>1.816825205966892</v>
       </c>
       <c r="D480" t="n">
-        <v>0.5713984995294877</v>
+        <v>0.5713984999999996</v>
       </c>
       <c r="E480" t="n">
-        <v>0.805691243571351</v>
+        <v>0.8056912436456862</v>
       </c>
       <c r="F480" t="n">
         <v>24</v>
@@ -11010,13 +11010,13 @@
         </is>
       </c>
       <c r="C481" t="n">
-        <v>2.309792127048042</v>
+        <v>2.309792126963122</v>
       </c>
       <c r="D481" t="n">
-        <v>0.7499068333624356</v>
+        <v>0.7499068333333317</v>
       </c>
       <c r="E481" t="n">
-        <v>0.9781239336329806</v>
+        <v>0.9781239334838904</v>
       </c>
       <c r="F481" t="n">
         <v>24</v>
@@ -11032,13 +11032,13 @@
         </is>
       </c>
       <c r="C482" t="n">
-        <v>2.058944363752317</v>
+        <v>2.058944363900097</v>
       </c>
       <c r="D482" t="n">
-        <v>0.6738806666181616</v>
+        <v>0.673880666666668</v>
       </c>
       <c r="E482" t="n">
-        <v>0.9387264264470884</v>
+        <v>0.9387264265148466</v>
       </c>
       <c r="F482" t="n">
         <v>24</v>
@@ -11054,13 +11054,13 @@
         </is>
       </c>
       <c r="C483" t="n">
-        <v>2.720428876002438</v>
+        <v>2.720428875779035</v>
       </c>
       <c r="D483" t="n">
-        <v>0.8999890000727607</v>
+        <v>0.8999890000000011</v>
       </c>
       <c r="E483" t="n">
-        <v>1.31602332949042</v>
+        <v>1.316023329442657</v>
       </c>
       <c r="F483" t="n">
         <v>24</v>
@@ -11076,13 +11076,13 @@
         </is>
       </c>
       <c r="C484" t="n">
-        <v>14.0273019451349</v>
+        <v>14.02730194476839</v>
       </c>
       <c r="D484" t="n">
-        <v>2.184989000092161</v>
+        <v>2.184988999975746</v>
       </c>
       <c r="E484" t="n">
-        <v>5.163609395404941</v>
+        <v>5.163609395362274</v>
       </c>
       <c r="F484" t="n">
         <v>24</v>
@@ -11098,13 +11098,13 @@
         </is>
       </c>
       <c r="C485" t="n">
-        <v>0.6788984110535183</v>
+        <v>0.6788984108598478</v>
       </c>
       <c r="D485" t="n">
-        <v>0.1710860000485073</v>
+        <v>0.1710860000000009</v>
       </c>
       <c r="E485" t="n">
-        <v>0.2342714831696127</v>
+        <v>0.234271483121614</v>
       </c>
       <c r="F485" t="n">
         <v>24</v>
@@ -11120,13 +11120,13 @@
         </is>
       </c>
       <c r="C486" t="n">
-        <v>0.5700604789766229</v>
+        <v>0.5700604792454683</v>
       </c>
       <c r="D486" t="n">
-        <v>0.143210999932091</v>
+        <v>0.143211</v>
       </c>
       <c r="E486" t="n">
-        <v>0.1761260920449694</v>
+        <v>0.1761260920590702</v>
       </c>
       <c r="F486" t="n">
         <v>24</v>
@@ -11142,13 +11142,13 @@
         </is>
       </c>
       <c r="C487" t="n">
-        <v>0.5379507658766585</v>
+        <v>0.5379507660719119</v>
       </c>
       <c r="D487" t="n">
-        <v>0.1353889999514924</v>
+        <v>0.1353889999999988</v>
       </c>
       <c r="E487" t="n">
-        <v>0.193575591206699</v>
+        <v>0.1935755913607562</v>
       </c>
       <c r="F487" t="n">
         <v>24</v>
@@ -11164,13 +11164,13 @@
         </is>
       </c>
       <c r="C488" t="n">
-        <v>1.255264401153645</v>
+        <v>1.255264401427499</v>
       </c>
       <c r="D488" t="n">
-        <v>0.3090139999320902</v>
+        <v>0.3090139999999992</v>
       </c>
       <c r="E488" t="n">
-        <v>0.5762220393225711</v>
+        <v>0.5762220393540427</v>
       </c>
       <c r="F488" t="n">
         <v>24</v>
@@ -11186,13 +11186,13 @@
         </is>
       </c>
       <c r="C489" t="n">
-        <v>5.078682437312635</v>
+        <v>5.078682437731272</v>
       </c>
       <c r="D489" t="n">
-        <v>1.008197333265423</v>
+        <v>1.008197333333332</v>
       </c>
       <c r="E489" t="n">
-        <v>2.284497509409643</v>
+        <v>2.284497509615043</v>
       </c>
       <c r="F489" t="n">
         <v>24</v>
@@ -11208,13 +11208,13 @@
         </is>
       </c>
       <c r="C490" t="n">
-        <v>0.8531155601166993</v>
+        <v>0.8531155599279641</v>
       </c>
       <c r="D490" t="n">
-        <v>0.2159193333818394</v>
+        <v>0.215919333333333</v>
       </c>
       <c r="E490" t="n">
-        <v>0.2755412168654326</v>
+        <v>0.2755412168272953</v>
       </c>
       <c r="F490" t="n">
         <v>24</v>
@@ -11230,13 +11230,13 @@
         </is>
       </c>
       <c r="C491" t="n">
-        <v>0.8773724703396114</v>
+        <v>0.8773724706084831</v>
       </c>
       <c r="D491" t="n">
-        <v>0.2207651665987565</v>
+        <v>0.2207651666666655</v>
       </c>
       <c r="E491" t="n">
-        <v>0.2649557984748707</v>
+        <v>0.2649557985538962</v>
       </c>
       <c r="F491" t="n">
         <v>24</v>
@@ -11252,13 +11252,13 @@
         </is>
       </c>
       <c r="C492" t="n">
-        <v>0.8597208144952381</v>
+        <v>0.8597208146867571</v>
       </c>
       <c r="D492" t="n">
-        <v>0.2170681666181619</v>
+        <v>0.2170681666666683</v>
       </c>
       <c r="E492" t="n">
-        <v>0.2888803700879717</v>
+        <v>0.2888803700853825</v>
       </c>
       <c r="F492" t="n">
         <v>24</v>
@@ -11274,13 +11274,13 @@
         </is>
       </c>
       <c r="C493" t="n">
-        <v>0.6097132763753312</v>
+        <v>0.6097132766534398</v>
       </c>
       <c r="D493" t="n">
-        <v>0.1542288694943577</v>
+        <v>0.1542288695652192</v>
       </c>
       <c r="E493" t="n">
-        <v>0.198362620235416</v>
+        <v>0.1983626202620297</v>
       </c>
       <c r="F493" t="n">
         <v>23</v>
